--- a/Supplementary_Table_S1_per_genome_results.xlsx
+++ b/Supplementary_Table_S1_per_genome_results.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -98,6 +98,9 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -138,7 +141,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -248,6 +251,7 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,12 +547,16 @@
     <row r="1" ht="15.75" customHeight="1" s="20">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>Colistin resistant E. coli genomes from Africa in NCBI Pathogen Detection</t>
+          <t>Colistin resistant E. coli genomes from Africa in NCBI Pathogen Detection (v2, 127 genomes)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="20">
-      <c r="A2" s="22" t="n"/>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Source: NCBI Pathogen Detection build PDG000000004.6345 (published 2026-10-06), per-isolate metadata table retrieved in full and country assigned locally. Supersedes the v1 cohort of 118 genomes, which was retrieved on 26 September 2026 by filtering on a 45-name African country list at query time; that list omitted nine of the 54 African Union member states, including South Africa, the Central African Republic and the Democratic Republic of the Congo, and nine genomes were missed as a result. All 118 v1 genomes are retained here and none was dropped.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="20">
       <c r="A3" s="22" t="inlineStr">
@@ -705,2601 +713,2620 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="9"/>
+    <col width="46" customWidth="1" style="20" min="1" max="1"/>
+    <col width="15" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15" customWidth="1" style="20" min="3" max="3"/>
+    <col width="15" customWidth="1" style="20" min="4" max="4"/>
+    <col width="15" customWidth="1" style="20" min="5" max="5"/>
+    <col width="15" customWidth="1" style="20" min="6" max="6"/>
+    <col width="15" customWidth="1" style="20" min="7" max="7"/>
+    <col width="15" customWidth="1" style="20" min="8" max="8"/>
+    <col width="15" customWidth="1" style="20" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="20">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>Genomes by country and sector</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="25" t="n"/>
-    </row>
-    <row r="2" ht="31.5" customHeight="1" s="20">
-      <c r="A2" s="27" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>Poultry</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>Food (non-poultry)</t>
         </is>
       </c>
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="G2" s="27" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H2" s="27" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I2" s="27" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>With Illumina reads</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="20">
-      <c r="A3" s="25" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="B3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H3" s="25">
+      <c r="B3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H3">
         <f>SUM(B3:G3)</f>
         <v/>
       </c>
-      <c r="I3" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A3,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="20">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="I3">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="B4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H4" s="25">
+      <c r="B4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H4">
         <f>SUM(B4:G4)</f>
         <v/>
       </c>
-      <c r="I4" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A4,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="20">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="I4">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUM(B5:G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUM(B6:G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>SUM(B5:G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A5,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="20">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="B7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(B7:G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="B6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>SUM(B6:G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A6,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="20">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="B8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUM(B8:G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="B7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>SUM(B7:G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A7,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="20">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="B9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUM(B9:G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="B8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>SUM(B8:G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A8,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="20">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="B10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(B10:G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
-      <c r="B9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H9" s="25">
-        <f>SUM(B9:G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A9,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="20">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="B11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(B11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H10" s="25">
-        <f>SUM(B10:G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A10,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="20">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="B12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(B12:G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="B11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>SUM(B11:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A11,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="20">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="B13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(B13:G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(B14:G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H12" s="25">
-        <f>SUM(B12:G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A12,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="20">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUM(B15:G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="B13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
-        <f>SUM(B13:G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A13,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="20">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="B16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>SUM(B16:G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H14" s="25">
-        <f>SUM(B14:G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A14,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="20">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="B17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>SUM(B17:G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="B15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,B$2)</f>
-        <v/>
-      </c>
-      <c r="C15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,C$2)</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,D$2)</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,E$2)</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,F$2)</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$O$2:$O$119,G$2)</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
-        <f>SUM(B15:G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A15,Isolates!$G$2:$G$119,"SRA Illumina PE reads")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="20">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="B18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,B$2)</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,C$2)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,D$2)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,E$2)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,F$2)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,G$2)</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(B18:G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="24">
-        <f>SUM(B3:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="24">
-        <f>SUM(C3:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="24">
-        <f>SUM(D3:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="24">
-        <f>SUM(E3:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="24">
-        <f>SUM(F3:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="24">
-        <f>SUM(G3:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="24">
-        <f>SUM(H3:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="24">
-        <f>SUM(I3:I15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="20">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="20">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B19">
+        <f>SUM(B3:B18)</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>SUM(C3:C18)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>SUM(D3:D18)</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>SUM(E3:E18)</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>SUM(F3:F18)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>SUM(G3:G18)</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUM(H3:H18)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>SUM(I3:I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Genomes by mcr variant and sector (a genome with two variants is counted under each)</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
-    </row>
-    <row r="19" ht="31.5" customHeight="1" s="20">
-      <c r="A19" s="27" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>mcr variant</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Poultry</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>Food (non-poultry)</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G22" s="37" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H22" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="20">
-      <c r="A20" s="25" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>mcr-1</t>
         </is>
       </c>
-      <c r="B20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A20&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="25">
-        <f>SUM(B20:G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="25" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="20">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="B21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A21&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H21" s="25">
-        <f>SUM(B21:G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="25" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="20">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="B23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>SUM(B23:G23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>SUM(B24:G24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>mcr-1.5</t>
         </is>
       </c>
-      <c r="B22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G22" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A22&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H22" s="25">
-        <f>SUM(B22:G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="25" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="20">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="B25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>SUM(B25:G25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="B23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G23" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H23" s="25">
-        <f>SUM(B23:G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="20">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="B26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>SUM(B26:G26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="B24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H24" s="25">
-        <f>SUM(B24:G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="25" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="20">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="B27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>SUM(B27:G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>mcr-9.2</t>
         </is>
       </c>
-      <c r="B25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G25" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H25" s="25">
-        <f>SUM(B25:G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="25" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="20">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="B28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>SUM(B28:G28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>mcr-10.1</t>
         </is>
       </c>
-      <c r="B26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,B$19)</f>
-        <v/>
-      </c>
-      <c r="C26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,C$19)</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,D$19)</f>
-        <v/>
-      </c>
-      <c r="E26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,E$19)</f>
-        <v/>
-      </c>
-      <c r="F26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,F$19)</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$119,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$119,G$19)</f>
-        <v/>
-      </c>
-      <c r="H26" s="25">
-        <f>SUM(B26:G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="25" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="20">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="B29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
+        <v/>
+      </c>
+      <c r="E29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
+        <v/>
+      </c>
+      <c r="F29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>SUM(B29:G29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Note: "mcr-1" and "mcr-9" without an allele number are AMRFinderPlus calls where the allele could not be resolved (partial or divergent hit).</t>
         </is>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="20">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="25" t="n"/>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="20">
-      <c r="A29" s="26" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>Poultry genomes by niche and country</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="25" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="25" t="n"/>
-      <c r="G29" s="25" t="n"/>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="25" t="n"/>
-    </row>
-    <row r="30" ht="31.5" customHeight="1" s="20">
-      <c r="A30" s="27" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>Live bird (faeces/cloaca/organ)</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>Poultry farm environment</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>Poultry drinking water</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>Poultry meat/carcass</t>
         </is>
       </c>
-      <c r="F30" s="27" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="20">
-      <c r="A31" s="25" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="B31" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A31,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A31,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A31,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A31,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="25">
-        <f>SUM(B31:E31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="25" t="n"/>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="20">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="B34">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>SUM(B34:E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="B32" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A32,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C32" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A32,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D32" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A32,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E32" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A32,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F32" s="25">
-        <f>SUM(B32:E32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="20">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="B35">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>SUM(B35:E35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B33" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A33,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C33" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A33,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D33" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A33,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E33" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A33,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F33" s="25">
-        <f>SUM(B33:E33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="25" t="n"/>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="20">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="B36">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C36">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D36">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>SUM(B36:E36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="B34" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A34,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C34" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A34,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D34" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A34,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E34" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A34,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F34" s="25">
-        <f>SUM(B34:E34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="20">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="B37">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C37">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D37">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>SUM(B37:E37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B35" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A35,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C35" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A35,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D35" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A35,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E35" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A35,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F35" s="25">
-        <f>SUM(B35:E35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="25" t="n"/>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="25" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="20">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="B38">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C38">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D38">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>SUM(B38:E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B36" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A36,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C36" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A36,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D36" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A36,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E36" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A36,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F36" s="25">
-        <f>SUM(B36:E36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="20">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="B39">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C39">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D39">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E39">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>SUM(B39:E39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="B37" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A37,Isolates!$P$2:$P$119,B$30)</f>
-        <v/>
-      </c>
-      <c r="C37" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A37,Isolates!$P$2:$P$119,C$30)</f>
-        <v/>
-      </c>
-      <c r="D37" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A37,Isolates!$P$2:$P$119,D$30)</f>
-        <v/>
-      </c>
-      <c r="E37" s="25">
-        <f>COUNTIFS(Isolates!$I$2:$I$119,$A37,Isolates!$P$2:$P$119,E$30)</f>
-        <v/>
-      </c>
-      <c r="F37" s="25">
-        <f>SUM(B37:E37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="20">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="B40">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,B$33)</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,C$33)</f>
+        <v/>
+      </c>
+      <c r="D40">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,D$33)</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,E$33)</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>SUM(B40:E40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>Genomes by sequence type (Achtman) and sector, STs seen in two or more genomes</t>
         </is>
       </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="20">
-      <c r="A40" s="24" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>Poultry</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D43" s="37" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>Food (non-poultry)</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="G43" s="37" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H40" s="24" t="inlineStr">
+      <c r="H43" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I40" s="25" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="20">
-      <c r="A41" s="25" t="n">
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>46</v>
       </c>
-      <c r="B41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A41,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="25">
-        <f>SUM(B41:G41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="25" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="20">
-      <c r="A42" s="25" t="n">
+      <c r="B44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H44">
+        <f>SUM(B44:G44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>155</v>
       </c>
-      <c r="B42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G42" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A42,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H42" s="25">
-        <f>SUM(B42:G42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="25" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="20">
-      <c r="A43" s="25" t="n">
+      <c r="B45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>SUM(B45:G45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>162</v>
+      </c>
+      <c r="B46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H46">
+        <f>SUM(B46:G46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>10</v>
       </c>
-      <c r="B43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G43" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A43,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H43" s="25">
-        <f>SUM(B43:G43)</f>
-        <v/>
-      </c>
-      <c r="I43" s="25" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="20">
-      <c r="A44" s="25" t="n">
-        <v>162</v>
-      </c>
-      <c r="B44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G44" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A44,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H44" s="25">
-        <f>SUM(B44:G44)</f>
-        <v/>
-      </c>
-      <c r="I44" s="25" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="20">
-      <c r="A45" s="25" t="n">
+      <c r="B47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H47">
+        <f>SUM(B47:G47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>69</v>
+      </c>
+      <c r="B48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H48">
+        <f>SUM(B48:G48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>117</v>
       </c>
-      <c r="B45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G45" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A45,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H45" s="25">
-        <f>SUM(B45:G45)</f>
-        <v/>
-      </c>
-      <c r="I45" s="25" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="20">
-      <c r="A46" s="25" t="n">
+      <c r="B49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H49">
+        <f>SUM(B49:G49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>224</v>
       </c>
-      <c r="B46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G46" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A46,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H46" s="25">
-        <f>SUM(B46:G46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="25" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="20">
-      <c r="A47" s="25" t="n">
+      <c r="B50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H50">
+        <f>SUM(B50:G50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
         <v>616</v>
       </c>
-      <c r="B47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G47" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A47,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H47" s="25">
-        <f>SUM(B47:G47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="25" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="20">
-      <c r="A48" s="25" t="n">
+      <c r="B51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H51">
+        <f>SUM(B51:G51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>3941</v>
       </c>
-      <c r="B48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G48" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A48,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H48" s="25">
-        <f>SUM(B48:G48)</f>
-        <v/>
-      </c>
-      <c r="I48" s="25" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="20">
-      <c r="A49" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="B49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G49" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A49,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H49" s="25">
-        <f>SUM(B49:G49)</f>
-        <v/>
-      </c>
-      <c r="I49" s="25" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="20">
-      <c r="A50" s="25" t="n">
+      <c r="B52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H52">
+        <f>SUM(B52:G52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>226</v>
+      </c>
+      <c r="B53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H53">
+        <f>SUM(B53:G53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101</v>
+      </c>
+      <c r="B54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H54">
+        <f>SUM(B54:G54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>93</v>
       </c>
-      <c r="B50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G50" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A50,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H50" s="25">
-        <f>SUM(B50:G50)</f>
-        <v/>
-      </c>
-      <c r="I50" s="25" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="20">
-      <c r="A51" s="25" t="n">
-        <v>101</v>
-      </c>
-      <c r="B51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G51" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A51,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H51" s="25">
-        <f>SUM(B51:G51)</f>
-        <v/>
-      </c>
-      <c r="I51" s="25" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="20">
-      <c r="A52" s="25" t="n">
+      <c r="B55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H55">
+        <f>SUM(B55:G55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>410</v>
       </c>
-      <c r="B52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G52" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A52,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H52" s="25">
-        <f>SUM(B52:G52)</f>
-        <v/>
-      </c>
-      <c r="I52" s="25" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="20">
-      <c r="A53" s="25" t="n">
+      <c r="B56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>SUM(B56:G56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>744</v>
       </c>
-      <c r="B53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G53" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A53,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H53" s="25">
-        <f>SUM(B53:G53)</f>
-        <v/>
-      </c>
-      <c r="I53" s="25" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="20">
-      <c r="A54" s="25" t="n">
+      <c r="B57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>SUM(B57:G57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
         <v>1011</v>
       </c>
-      <c r="B54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G54" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A54,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H54" s="25">
-        <f>SUM(B54:G54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="25" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="20">
-      <c r="A55" s="25" t="n">
+      <c r="B58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>SUM(B58:G58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
         <v>38</v>
       </c>
-      <c r="B55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G55" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A55,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H55" s="25">
-        <f>SUM(B55:G55)</f>
-        <v/>
-      </c>
-      <c r="I55" s="25" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="20">
-      <c r="A56" s="25" t="n">
+      <c r="B59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H59">
+        <f>SUM(B59:G59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
         <v>167</v>
       </c>
-      <c r="B56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G56" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A56,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H56" s="25">
-        <f>SUM(B56:G56)</f>
-        <v/>
-      </c>
-      <c r="I56" s="25" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="20">
-      <c r="A57" s="25" t="n">
+      <c r="B60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>SUM(B60:G60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
         <v>189</v>
       </c>
-      <c r="B57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G57" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A57,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H57" s="25">
-        <f>SUM(B57:G57)</f>
-        <v/>
-      </c>
-      <c r="I57" s="25" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="20">
-      <c r="A58" s="25" t="n">
+      <c r="B61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H61">
+        <f>SUM(B61:G61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
         <v>191</v>
       </c>
-      <c r="B58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G58" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A58,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H58" s="25">
-        <f>SUM(B58:G58)</f>
-        <v/>
-      </c>
-      <c r="I58" s="25" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="20">
-      <c r="A59" s="25" t="n">
+      <c r="B62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H62">
+        <f>SUM(B62:G62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>297</v>
+      </c>
+      <c r="B63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H63">
+        <f>SUM(B63:G63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
         <v>354</v>
       </c>
-      <c r="B59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G59" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A59,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H59" s="25">
-        <f>SUM(B59:G59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="25" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="20">
-      <c r="A60" s="25" t="n">
+      <c r="B64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H64">
+        <f>SUM(B64:G64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
         <v>484</v>
       </c>
-      <c r="B60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G60" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A60,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H60" s="25">
-        <f>SUM(B60:G60)</f>
-        <v/>
-      </c>
-      <c r="I60" s="25" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="20">
-      <c r="A61" s="25" t="n">
+      <c r="B65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H65">
+        <f>SUM(B65:G65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
         <v>1266</v>
       </c>
-      <c r="B61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G61" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A61,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H61" s="25">
-        <f>SUM(B61:G61)</f>
-        <v/>
-      </c>
-      <c r="I61" s="25" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="20">
-      <c r="A62" s="25" t="n">
+      <c r="B66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H66">
+        <f>SUM(B66:G66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
         <v>2485</v>
       </c>
-      <c r="B62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G62" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A62,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H62" s="25">
-        <f>SUM(B62:G62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="25" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="20">
-      <c r="A63" s="25" t="n">
+      <c r="B67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H67">
+        <f>SUM(B67:G67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
         <v>8492</v>
       </c>
-      <c r="B63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G63" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A63,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H63" s="25">
-        <f>SUM(B63:G63)</f>
-        <v/>
-      </c>
-      <c r="I63" s="25" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="20">
-      <c r="A64" s="25" t="n">
+      <c r="B68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H68">
+        <f>SUM(B68:G68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
         <v>9697</v>
       </c>
-      <c r="B64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G64" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A64,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H64" s="25">
-        <f>SUM(B64:G64)</f>
-        <v/>
-      </c>
-      <c r="I64" s="25" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="20">
-      <c r="A65" s="25" t="inlineStr">
+      <c r="B69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H69">
+        <f>SUM(B69:G69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Untypeable</t>
         </is>
       </c>
-      <c r="B65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,B$40)</f>
-        <v/>
-      </c>
-      <c r="C65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,C$40)</f>
-        <v/>
-      </c>
-      <c r="D65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,D$40)</f>
-        <v/>
-      </c>
-      <c r="E65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,E$40)</f>
-        <v/>
-      </c>
-      <c r="F65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,F$40)</f>
-        <v/>
-      </c>
-      <c r="G65" s="25">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$119,$A65,Isolates!$O$2:$O$119,G$40)</f>
-        <v/>
-      </c>
-      <c r="H65" s="25">
-        <f>SUM(B65:G65)</f>
-        <v/>
-      </c>
-      <c r="I65" s="25" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="20">
-      <c r="A66" s="25" t="inlineStr">
+      <c r="B70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,B$43)</f>
+        <v/>
+      </c>
+      <c r="C70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,C$43)</f>
+        <v/>
+      </c>
+      <c r="D70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,D$43)</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,E$43)</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,F$43)</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,G$43)</f>
+        <v/>
+      </c>
+      <c r="H70">
+        <f>SUM(B70:G70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Other STs (single genome)</t>
         </is>
       </c>
-      <c r="B66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,B$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(B41:B65)</f>
-        <v/>
-      </c>
-      <c r="C66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,C$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(C41:C65)</f>
-        <v/>
-      </c>
-      <c r="D66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,D$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(D41:D65)</f>
-        <v/>
-      </c>
-      <c r="E66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,E$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(E41:E65)</f>
-        <v/>
-      </c>
-      <c r="F66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,F$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(F41:F65)</f>
-        <v/>
-      </c>
-      <c r="G66" s="25">
-        <f>COUNTIFS(Isolates!$O$2:$O$119,G$40,Isolates!$Z$2:$Z$119,"&lt;&gt;")-SUM(G41:G65)</f>
-        <v/>
-      </c>
-      <c r="H66" s="25">
-        <f>SUM(B66:G66)</f>
-        <v/>
-      </c>
-      <c r="I66" s="25" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="20">
-      <c r="A67" s="25" t="inlineStr">
+      <c r="B71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,B$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(B44:B70)</f>
+        <v/>
+      </c>
+      <c r="C71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,C$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(C44:C70)</f>
+        <v/>
+      </c>
+      <c r="D71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,D$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(D44:D70)</f>
+        <v/>
+      </c>
+      <c r="E71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,E$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(E44:E70)</f>
+        <v/>
+      </c>
+      <c r="F71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,F$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(F44:F70)</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,G$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(G44:G70)</f>
+        <v/>
+      </c>
+      <c r="H71">
+        <f>SUM(B71:G71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>Total typed or untypeable</t>
         </is>
       </c>
-      <c r="B67" s="25">
-        <f>SUM(B41:B66)</f>
-        <v/>
-      </c>
-      <c r="C67" s="25">
-        <f>SUM(C41:C66)</f>
-        <v/>
-      </c>
-      <c r="D67" s="25">
-        <f>SUM(D41:D66)</f>
-        <v/>
-      </c>
-      <c r="E67" s="25">
-        <f>SUM(E41:E66)</f>
-        <v/>
-      </c>
-      <c r="F67" s="25">
-        <f>SUM(F41:F66)</f>
-        <v/>
-      </c>
-      <c r="G67" s="25">
-        <f>SUM(G41:G66)</f>
-        <v/>
-      </c>
-      <c r="H67" s="25">
-        <f>SUM(H41:H66)</f>
-        <v/>
-      </c>
-      <c r="I67" s="25" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="20">
-      <c r="A68" s="25" t="n"/>
-      <c r="B68" s="25" t="n"/>
-      <c r="C68" s="25" t="n"/>
-      <c r="D68" s="25" t="n"/>
-      <c r="E68" s="25" t="n"/>
-      <c r="F68" s="25" t="n"/>
-      <c r="G68" s="25" t="n"/>
-      <c r="H68" s="25" t="n"/>
-      <c r="I68" s="25" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="20">
-      <c r="A69" s="24" t="inlineStr">
-        <is>
-          <t>Genomes by plasmid replicon linked to mcr and sector (wildcard match on the Isolates replicon column; mixed MOB-Recon bins count under each family)</t>
-        </is>
-      </c>
-      <c r="B69" s="25" t="n"/>
-      <c r="C69" s="25" t="n"/>
-      <c r="D69" s="25" t="n"/>
-      <c r="E69" s="25" t="n"/>
-      <c r="F69" s="25" t="n"/>
-      <c r="G69" s="25" t="n"/>
-      <c r="H69" s="25" t="n"/>
-      <c r="I69" s="25" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="20">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="B72">
+        <f>SUM(B44:B71)</f>
+        <v/>
+      </c>
+      <c r="C72">
+        <f>SUM(C44:C71)</f>
+        <v/>
+      </c>
+      <c r="D72">
+        <f>SUM(D44:D71)</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>SUM(E44:E71)</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>SUM(F44:F71)</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>SUM(G44:G71)</f>
+        <v/>
+      </c>
+      <c r="H72">
+        <f>SUM(H44:H71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="37" t="inlineStr">
+        <is>
+          <t>Genomes by plasmid replicon linked to mcr and sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>Replicon</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
+      <c r="B75" s="37" t="inlineStr">
         <is>
           <t>Poultry</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C75" s="37" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="D70" s="24" t="inlineStr">
+      <c r="D75" s="37" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="E70" s="24" t="inlineStr">
+      <c r="E75" s="37" t="inlineStr">
         <is>
           <t>Food (non-poultry)</t>
         </is>
       </c>
-      <c r="F70" s="24" t="inlineStr">
+      <c r="F75" s="37" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="G70" s="24" t="inlineStr">
+      <c r="G75" s="37" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="H70" s="24" t="inlineStr">
+      <c r="H75" s="37" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I70" s="25" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="20">
-      <c r="A71" s="25" t="inlineStr">
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="B71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G71" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncI2*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H71" s="25">
-        <f>SUM(B71:G71)</f>
-        <v/>
-      </c>
-      <c r="I71" s="25" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="20">
-      <c r="A72" s="25" t="inlineStr">
+      <c r="B76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H76">
+        <f>SUM(B76:G76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="B72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G72" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncX4*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H72" s="25">
-        <f>SUM(B72:G72)</f>
-        <v/>
-      </c>
-      <c r="I72" s="25" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="20">
-      <c r="A73" s="25" t="inlineStr">
+      <c r="B77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H77">
+        <f>SUM(B77:G77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>IncHI2</t>
         </is>
       </c>
-      <c r="B73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G73" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI2*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H73" s="25">
-        <f>SUM(B73:G73)</f>
-        <v/>
-      </c>
-      <c r="I73" s="25" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="20">
-      <c r="A74" s="25" t="inlineStr">
+      <c r="B78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>SUM(B78:G78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>IncHI1</t>
         </is>
       </c>
-      <c r="B74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G74" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncHI1*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H74" s="25">
-        <f>SUM(B74:G74)</f>
-        <v/>
-      </c>
-      <c r="I74" s="25" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="20">
-      <c r="A75" s="25" t="inlineStr">
+      <c r="B79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H79">
+        <f>SUM(B79:G79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>IncF (FII/FIB/FIA)</t>
         </is>
       </c>
-      <c r="B75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G75" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"*IncF*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H75" s="25">
-        <f>SUM(B75:G75)</f>
-        <v/>
-      </c>
-      <c r="I75" s="25" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="20">
-      <c r="A76" s="25" t="inlineStr">
+      <c r="B80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>SUM(B80:G80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Other rep cluster (no Inc type)</t>
         </is>
       </c>
-      <c r="B76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G76" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"rep_cluster*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H76" s="25">
-        <f>SUM(B76:G76)</f>
-        <v/>
-      </c>
-      <c r="I76" s="25" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="20">
-      <c r="A77" s="25" t="inlineStr">
+      <c r="B81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H81">
+        <f>SUM(B81:G81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Plasmid, no replicon detected</t>
         </is>
       </c>
-      <c r="B77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G77" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Plasmid, no replicon*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H77" s="25">
-        <f>SUM(B77:G77)</f>
-        <v/>
-      </c>
-      <c r="I77" s="25" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="20">
-      <c r="A78" s="25" t="inlineStr">
+      <c r="B82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H82">
+        <f>SUM(B82:G82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Chromosomal or unresolved</t>
         </is>
       </c>
-      <c r="B78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,B$70)</f>
-        <v/>
-      </c>
-      <c r="C78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,C$70)</f>
-        <v/>
-      </c>
-      <c r="D78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,D$70)</f>
-        <v/>
-      </c>
-      <c r="E78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,E$70)</f>
-        <v/>
-      </c>
-      <c r="F78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,F$70)</f>
-        <v/>
-      </c>
-      <c r="G78" s="25">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$119,"Chromosomal*",Isolates!$O$2:$O$119,G$70)</f>
-        <v/>
-      </c>
-      <c r="H78" s="25">
-        <f>SUM(B78:G78)</f>
-        <v/>
-      </c>
-      <c r="I78" s="25" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="20">
-      <c r="A79" s="25" t="n"/>
-      <c r="B79" s="25" t="n"/>
-      <c r="C79" s="25" t="n"/>
-      <c r="D79" s="25" t="n"/>
-      <c r="E79" s="25" t="n"/>
-      <c r="F79" s="25" t="n"/>
-      <c r="G79" s="25" t="n"/>
-      <c r="H79" s="25" t="n"/>
-      <c r="I79" s="25" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="20">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>Note: ST and replicon columns were filled from the Galaxy run (usegalaxy.eu, histories "mcr Africa A reads", "mcr Africa B assemblies", "mcr Africa C typing"). Per-genome detail is in the Galaxy_results sheet.</t>
-        </is>
-      </c>
-      <c r="B80" s="25" t="n"/>
-      <c r="C80" s="25" t="n"/>
-      <c r="D80" s="25" t="n"/>
-      <c r="E80" s="25" t="n"/>
-      <c r="F80" s="25" t="n"/>
-      <c r="G80" s="25" t="n"/>
-      <c r="H80" s="25" t="n"/>
-      <c r="I80" s="25" t="n"/>
+      <c r="B83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,B$75)</f>
+        <v/>
+      </c>
+      <c r="C83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,C$75)</f>
+        <v/>
+      </c>
+      <c r="D83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,D$75)</f>
+        <v/>
+      </c>
+      <c r="E83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,E$75)</f>
+        <v/>
+      </c>
+      <c r="F83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,F$75)</f>
+        <v/>
+      </c>
+      <c r="G83">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,G$75)</f>
+        <v/>
+      </c>
+      <c r="H83">
+        <f>SUM(B83:G83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Note: ST and replicon columns were filled from the Galaxy_results sheet. Rows beyond genome 118 were added by the corrected retrieval in v2 and typed in the Galaxy history "mcr Africa D typing".</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3309,7 +3336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF119"/>
+  <dimension ref="A1:AF128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="19" min="1" max="2"/>
@@ -3594,10 +3621,10 @@
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="AF2" s="19" t="inlineStr">
@@ -17228,10 +17255,10 @@
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD116" t="n">
+      <c r="AD116" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE116" t="n">
+      <c r="AE116" s="19" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -17588,6 +17615,954 @@
       <c r="AF119" s="19" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PDT003089299.1</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SAMEA120683848</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PRJEB104706</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GCA_977857845.1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>blaCTX-M-55</t>
+        </is>
+      </c>
+      <c r="X120" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>aadA1 aadA2 aph(3')-Ia blaCTX-M-55 cmlA1 dfrA12 gyrA_D87N gyrA_S83L mcr-1.1 parC_S80I qnrS13 sul3 tet(A) tet(M)</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>226</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>IncX4</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). mcr-1.1 and IncX4 on the same 32.7 kb contig.</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD120" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PDT003089301.1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SAMEA120683850</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PRJEB104706</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>GCA_977859995.1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Central African Republic</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>blaCTX-M-55</t>
+        </is>
+      </c>
+      <c r="X121" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>aadA1 aadA2 aph(3'')-Ib aph(3')-Ia aph(6)-Id blaCTX-M-55 cmlA1 dfrA12 erm(B) gyrA_D87N gyrA_S83L mcr-1.1 mph(A) parC_S80I qnrS13 sul1 sul2 sul3 tet(A) tet(B) tet(M)</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>226</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>IncX4</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Same ST and replicon as SAMEA120683848, same submission.</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD121" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PDT000640376.1</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SAMEA5988742</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PRJEB34702</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>GCA_902703155.1</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Eco04570</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>2016</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>clinical material</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X122" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>aph(3'')-Ib=PARTIAL_END_OF_CONTIG aph(6)-Id bleO dfrA14 gyrA_S83L mcr-1.1 oqxA oqxB sul2 tet(B)</t>
+        </is>
+      </c>
+      <c r="Z122" t="n">
+        <v>602</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>IncI2</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). mcr-1.1 and IncI2 on the same 56.2 kb contig.</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD122" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PDT000409988.1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SAMN09303237</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PRJNA412434</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GCA_003795445.1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>PN256E8</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>2016</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>pig</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>nares</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Other animal</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>blaCTX-M-55</t>
+        </is>
+      </c>
+      <c r="X123" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib3 aadA5 aph(6)-Id=PARTIAL_END_OF_CONTIG blaCTX-M-55 blaTEM=PARTIAL bleO dfrA17 floR fosA3 mcr-1.1 oqxA oqxB sul2 tet(A)</t>
+        </is>
+      </c>
+      <c r="Z123" t="n">
+        <v>9440</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>IncHI2A (MOB-Recon bin)</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Pig nasal isolate; mcr contig 2.9 kb, IncHI2 from MOB-Recon bin only.</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD123" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PDT000878268.1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SAMN14219481</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PRJNA609073</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>GCA_015208565.1</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D96_9</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>wastewater</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>environmental/other</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>mcr-9</t>
+        </is>
+      </c>
+      <c r="X124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>blaTEM-1 cyaA_S352T mcr-9=PARTIAL_END_OF_CONTIG tet(A)</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Chromosomal or unresolved (MOB-Recon)</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Wastewater mcr-9 on a 2.6 kb contig placed in the chromosome bin; unresolved.</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>|mcr-9|</t>
+        </is>
+      </c>
+      <c r="AD124" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PDT001428169.1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SAMN28613555</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PRJNA841695</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GCA_025336805.1</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Q0169</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Papio cynocephalus</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>fecal samples</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Other animal</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X125" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>blaTEM-1 cyaA_S352T mcr-1.1</t>
+        </is>
+      </c>
+      <c r="Z125" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Plasmid, no replicon detected (MOB-Recon)</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Wild baboon faeces; 2.5 kb mcr contig in a plasmid bin with no typeable replicon.</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD125" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PDT001428170.1</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SAMN28613556</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PRJNA841695</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GCA_025336825.1</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Q0170</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Papio cynocephalus</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>fecal samples</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Other animal</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X126" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>aadA1 aph(3'')-Ib aph(6)-Id blaTEM-1 catA1 cirA_N81TerfsTer0 dfrA1 gyrA_S83L mcr-1.1 mph(B) rdmCL sul1 sul2 tet(A)</t>
+        </is>
+      </c>
+      <c r="Z126" t="n">
+        <v>101</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>IncI2</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Wild baboon faeces; mcr-1.1 and IncI2 on the same 66.5 kb contig.</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD126" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PDT002034360.1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SAMN36943049</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PRJNA999080</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GCA_034465125.1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SRR25608269</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Short-read assembly (Shovill)</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>R2745-Af49</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>blaCTX-M-55</t>
+        </is>
+      </c>
+      <c r="X127" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib3 aadA1 blaCTX-M-55 blaTEM=PARTIAL blaTEM=PARTIAL_END_OF_CONTIG cirA_D84IfsTer16 dfrA15 floR fosA3 gyrA_D87N gyrA_S83L mcr-1.1 parC_S80I sul1 sul2 tet(A) tet(A)=PARTIAL_END_OF_CONTIG</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>226</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>IncHI2A/IncFIB (MOB-Recon bin, mixed replicons)</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Two mcr-1.1 calls on 2.6 kb and 2.7 kb contigs, one chromosome-binned and one in a mixed IncFIB/IncHI2A bin; counted once as unresolved.</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>|mcr-1.1|</t>
+        </is>
+      </c>
+      <c r="AD127" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PDT003000705.1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SAMN49772998</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PRJNA642017</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>GCA_053709775.1</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>GenBank assembly (no reads)</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>UPMP1740</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>2019</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Food (non-poultry)</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>mcr-9.1</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="X128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14 fosA3 mcr-9.1</t>
+        </is>
+      </c>
+      <c r="Z128" t="n">
+        <v>297</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Chromosomal or unresolved (MOB-Recon)</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Added by the corrected retrieval (v2). Cucumber isolate; mcr-9.1 on a 3.5 kb contig placed in the chromosome bin; unresolved.</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>|mcr-9.1|</t>
+        </is>
+      </c>
+      <c r="AD128" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -17605,7 +18580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="19" min="1" max="1"/>
@@ -19508,6 +20483,48 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SRR25608269</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SAMN36943049</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ILLUMINA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PAIRED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Short-read assembly (Shovill)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H45"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -19522,7 +20539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z119"/>
+  <dimension ref="A1:Z128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="19" min="1" max="2"/>
@@ -32427,6 +33444,940 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SAMEA120683848</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GCA_977857845.1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>127</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4775047</v>
+      </c>
+      <c r="H120" t="n">
+        <v>94422</v>
+      </c>
+      <c r="I120" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>CDWHFB010000042.1</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>IncX4_1</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>IncX4</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>MOBP</t>
+        </is>
+      </c>
+      <c r="W120" t="n">
+        <v>32730</v>
+      </c>
+      <c r="X120" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>ColpVC_1, IncFII_1, IncX1_1, IncX4_1, p0111_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SAMEA120683850</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>GCA_977859995.1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>360</v>
+      </c>
+      <c r="G121" t="n">
+        <v>5508014</v>
+      </c>
+      <c r="H121" t="n">
+        <v>72378</v>
+      </c>
+      <c r="I121" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>CDWHOZ010000048.1</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>IncX4_1</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>IncX4</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>MOBP</t>
+        </is>
+      </c>
+      <c r="W121" t="n">
+        <v>32686</v>
+      </c>
+      <c r="X121" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>Col(BS512)_1, ColpVC_1, IncFIA_1, IncFIB(AP001918)_1, IncFII_1, IncX1_1, IncX4_1, p0111_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SAMEA5988742</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GCA_902703155.1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>107</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5289460</v>
+      </c>
+      <c r="H122" t="n">
+        <v>204049</v>
+      </c>
+      <c r="I122" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>CACRYI010000026.1</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>IncI2_1_Delta</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>IncI2</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>MOBP</t>
+        </is>
+      </c>
+      <c r="W122" t="n">
+        <v>62892</v>
+      </c>
+      <c r="X122" t="n">
+        <v>602</v>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>adk(6) fumC(19) gyrB(33) icd(26) mdh(11) purA(8) recA(6)</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)_1, IncI1_1_Alpha, IncI2_1_Delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SAMN09303237</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GCA_003795445.1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>242</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4988197</v>
+      </c>
+      <c r="H123" t="n">
+        <v>85550</v>
+      </c>
+      <c r="I123" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>QJRZ01000018.1</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>IncHI2A, rep_cluster_1088</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>MOBH</t>
+        </is>
+      </c>
+      <c r="W123" t="n">
+        <v>250002</v>
+      </c>
+      <c r="X123" t="n">
+        <v>9440</v>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>adk(10) fumC(11) gyrB(4) icd(8) mdh(8) purA(724) recA(2)</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>IncHI2A_1, IncHI2_1, IncN_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SAMN14219481</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GCA_015208565.1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>216</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5321899</v>
+      </c>
+      <c r="H124" t="n">
+        <v>249887</v>
+      </c>
+      <c r="I124" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>FAIL CheckM2 contamination 6.00% (&gt;5% threshold)</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>mcr-9</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>mcr-9</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>BLASTX</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>99.74</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>99.21</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>JAAOAA010000190.1</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>mcr-9</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>mcr-9_1</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>chromosome</t>
+        </is>
+      </c>
+      <c r="X124" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>adk(21) fumC(35) gyrB(27) icd(6) mdh(5) purA(5) recA(4)</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>IncFIA_1, IncFIB(AP001918)_1, IncFIC(FII)_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SAMN28613555</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GCA_025336805.1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>343</v>
+      </c>
+      <c r="G125" t="n">
+        <v>5278367</v>
+      </c>
+      <c r="H125" t="n">
+        <v>155237</v>
+      </c>
+      <c r="I125" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>JAODFU010000074.1</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="W125" t="n">
+        <v>27806</v>
+      </c>
+      <c r="X125" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>adk(21) fumC(35) gyrB(27) icd(6) mdh(5) purA(5) recA(4)</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Col156_1, IncFII(29)_1, IncFII(pAMA1167-NDM-5)_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SAMN28613556</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GCA_025336825.1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5069550</v>
+      </c>
+      <c r="H126" t="n">
+        <v>354723</v>
+      </c>
+      <c r="I126" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>JAODFT010000018.1</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>IncI2_1_Delta</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>plasmid</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>IncI2</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>MOBP</t>
+        </is>
+      </c>
+      <c r="W126" t="n">
+        <v>68367</v>
+      </c>
+      <c r="X126" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>adk(43) fumC(41) gyrB(15) icd(18) mdh(11) purA(7) recA(6)</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)_1, IncI2_1_Delta, IncQ1_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SAMN36943049</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GCA_034465125.1</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>A (SRA reads)</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>214</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5295826</v>
+      </c>
+      <c r="H127" t="n">
+        <v>83445</v>
+      </c>
+      <c r="I127" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>DASMXT010000124.1 / DASMXT010000213.1</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>mcr-1.1_1</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>chromosome / plasmid</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>IncFIB, IncHI2A, rep_cluster_1088</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>MOBH</t>
+        </is>
+      </c>
+      <c r="W127" t="n">
+        <v>328273</v>
+      </c>
+      <c r="X127" t="n">
+        <v>226</v>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)_1, IncFII(pCoo)_1, IncHI2A_1, IncHI2_1, IncI1_1_Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SAMN49772998</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GCA_053709775.1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B (GenBank assembly)</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>205</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5100318</v>
+      </c>
+      <c r="H128" t="n">
+        <v>111077</v>
+      </c>
+      <c r="I128" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>mcr-9.1</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>mcr-9.1</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>ALLELEX</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>JBSKJU010000076.1</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>mcr-9.1</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>mcr-9.1_1</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>chromosome</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>MOBP</t>
+        </is>
+      </c>
+      <c r="X128" t="n">
+        <v>297</v>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>adk(6) fumC(65) gyrB(32) icd(26) mdh(9) purA(8) recA(2)</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>IncI1_1_Alpha, IncI2_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Z119"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/Supplementary_Table_S1_per_genome_results.xlsx
+++ b/Supplementary_Table_S1_per_genome_results.xlsx
@@ -734,7 +734,7 @@
     <row r="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
-          <t>Genomes by country and sector</t>
+          <t>Analysed genomes by country and sector (126 of the 127 retrieved; GCA_015208565.1 excluded at quality control)</t>
         </is>
       </c>
     </row>
@@ -786,626 +786,626 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="B3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H3">
+      <c r="B3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H3" s="19">
         <f>SUM(B3:G3)</f>
         <v/>
       </c>
-      <c r="I3">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I3" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A3,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="B4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H4">
+      <c r="B4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H4" s="19">
         <f>SUM(B4:G4)</f>
         <v/>
       </c>
-      <c r="I4">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I4" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A4,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Central African Republic</t>
         </is>
       </c>
-      <c r="B5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H5">
+      <c r="B5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H5" s="19">
         <f>SUM(B5:G5)</f>
         <v/>
       </c>
-      <c r="I5">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I5" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A5,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Democratic Republic of the Congo</t>
         </is>
       </c>
-      <c r="B6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H6">
+      <c r="B6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H6" s="19">
         <f>SUM(B6:G6)</f>
         <v/>
       </c>
-      <c r="I6">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I6" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A6,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H7">
+      <c r="B7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H7" s="19">
         <f>SUM(B7:G7)</f>
         <v/>
       </c>
-      <c r="I7">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I7" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A7,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="B8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H8">
+      <c r="B8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
         <f>SUM(B8:G8)</f>
         <v/>
       </c>
-      <c r="I8">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I8" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A8,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="B9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H9">
+      <c r="B9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H9" s="19">
         <f>SUM(B9:G9)</f>
         <v/>
       </c>
-      <c r="I9">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I9" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A9,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="B10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H10">
+      <c r="B10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
         <f>SUM(B10:G10)</f>
         <v/>
       </c>
-      <c r="I10">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I10" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A10,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
-      <c r="B11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H11">
+      <c r="B11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H11" s="19">
         <f>SUM(B11:G11)</f>
         <v/>
       </c>
-      <c r="I11">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I11" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A11,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H12">
+      <c r="B12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
         <f>SUM(B12:G12)</f>
         <v/>
       </c>
-      <c r="I12">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I12" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A12,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="B13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H13">
+      <c r="B13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H13" s="19">
         <f>SUM(B13:G13)</f>
         <v/>
       </c>
-      <c r="I13">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I13" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A13,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="B14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H14">
+      <c r="B14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H14" s="19">
         <f>SUM(B14:G14)</f>
         <v/>
       </c>
-      <c r="I14">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I14" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A14,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H15">
+      <c r="B15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
         <f>SUM(B15:G15)</f>
         <v/>
       </c>
-      <c r="I15">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I15" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A15,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="B16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H16">
+      <c r="B16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H16" s="19">
         <f>SUM(B16:G16)</f>
         <v/>
       </c>
-      <c r="I16">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I16" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A16,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H17">
+      <c r="B17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H17" s="19">
         <f>SUM(B17:G17)</f>
         <v/>
       </c>
-      <c r="I17">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I17" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A17,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="B18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,B$2)</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,C$2)</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,D$2)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,E$2)</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,F$2)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,G$2)</f>
-        <v/>
-      </c>
-      <c r="H18">
+      <c r="B18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,B$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,C$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,D$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,E$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,F$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$O$2:$O$128,G$2,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
         <f>SUM(B18:G18)</f>
         <v/>
       </c>
-      <c r="I18">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$G$2:$G$128,"SRA Illumina PE reads")</f>
+      <c r="I18" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A18,Isolates!$G$2:$G$128,"SRA Illumina PE reads",Isolates!$AG$2:$AG$128,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -1415,43 +1415,44 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" s="19">
         <f>SUM(B3:B18)</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C19" s="19">
         <f>SUM(C3:C18)</f>
         <v/>
       </c>
-      <c r="D19">
+      <c r="D19" s="19">
         <f>SUM(D3:D18)</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E19" s="19">
         <f>SUM(E3:E18)</f>
         <v/>
       </c>
-      <c r="F19">
+      <c r="F19" s="19">
         <f>SUM(F3:F18)</f>
         <v/>
       </c>
-      <c r="G19">
+      <c r="G19" s="19">
         <f>SUM(G3:G18)</f>
         <v/>
       </c>
-      <c r="H19">
+      <c r="H19" s="19">
         <f>SUM(H3:H18)</f>
         <v/>
       </c>
-      <c r="I19">
+      <c r="I19" s="19">
         <f>SUM(I3:I18)</f>
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="37" t="inlineStr">
         <is>
-          <t>Genomes by mcr variant and sector (a genome with two variants is counted under each)</t>
+          <t>Analysed genomes by mcr variant and sector (a genome with two variants is counted under each)</t>
         </is>
       </c>
     </row>
@@ -1498,274 +1499,282 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>mcr-1</t>
         </is>
       </c>
-      <c r="B23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G23">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H23">
+      <c r="B23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A23&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H23" s="19">
         <f>SUM(B23:G23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A24&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
         <f>SUM(B24:G24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>mcr-1.5</t>
         </is>
       </c>
-      <c r="B25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H25">
+      <c r="B25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G25" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A25&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H25" s="19">
         <f>SUM(B25:G25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="B26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H26">
+      <c r="B26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A26&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
         <f>SUM(B26:G26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="B27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G27">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H27">
+      <c r="B27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A27&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
         <f>SUM(B27:G27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>mcr-9.2</t>
         </is>
       </c>
-      <c r="B28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H28">
+      <c r="B28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A28&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
         <f>SUM(B28:G28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>mcr-10.1</t>
         </is>
       </c>
-      <c r="B29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,B$22)</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,C$22)</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,D$22)</f>
-        <v/>
-      </c>
-      <c r="E29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,E$22)</f>
-        <v/>
-      </c>
-      <c r="F29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,F$22)</f>
-        <v/>
-      </c>
-      <c r="G29">
-        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,G$22)</f>
-        <v/>
-      </c>
-      <c r="H29">
+      <c r="B29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,B$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,C$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,D$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,E$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,F$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>COUNTIFS(Isolates!$AC$2:$AC$128,"*|"&amp;$A29&amp;"|*",Isolates!$O$2:$O$128,G$22,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
         <f>SUM(B29:G29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Note: "mcr-1" and "mcr-9" without an allele number are AMRFinderPlus calls where the allele could not be resolved (partial or divergent hit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Retrieval and quality control</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>Poultry genomes by niche and country</t>
-        </is>
+          <t>Genomes retrieved for build PDG000000004.6345</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B33" s="37" t="inlineStr">
-        <is>
-          <t>Live bird (faeces/cloaca/organ)</t>
-        </is>
+          <t>Excluded: CheckM2 contamination above the 5% ceiling</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
@@ -1789,194 +1798,195 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Genomes analysed</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>126</v>
+      </c>
+      <c r="C34" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A34,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
         <f>SUM(B34:E34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="B35">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C35">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E35">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Excluded accession</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>GCA_015208565.1 (SAMN14219481), 6.00% contamination</t>
+        </is>
+      </c>
+      <c r="C35" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A35,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
         <f>SUM(B35:E35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B36">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C36">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F36">
+      <c r="B36" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,B$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A36,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
         <f>SUM(B36:E36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="B37">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C37">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E37">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F37">
+      <c r="B37" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,B$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A37,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
         <f>SUM(B37:E37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B38">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C38">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E38">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F38">
+      <c r="B38" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,B$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A38,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
         <f>SUM(B38:E38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B39">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C39">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E39">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F39">
+      <c r="B39" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,B$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D39" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E39" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A39,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F39" s="19">
         <f>SUM(B39:E39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="B40">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,B$33)</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,C$33)</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,D$33)</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,E$33)</f>
-        <v/>
-      </c>
-      <c r="F40">
+      <c r="B40" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,B$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C40" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,C$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D40" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,D$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E40" s="19">
+        <f>COUNTIFS(Isolates!$I$2:$I$128,$A40,Isolates!$P$2:$P$128,E$33,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F40" s="19">
         <f>SUM(B40:E40)</f>
         <v/>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="37" t="inlineStr">
         <is>
@@ -2027,929 +2037,929 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="19" t="n">
         <v>46</v>
       </c>
-      <c r="B44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H44">
+      <c r="B44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G44" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A44,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H44" s="19">
         <f>SUM(B44:G44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="19" t="n">
         <v>155</v>
       </c>
-      <c r="B45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G45">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H45">
+      <c r="B45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G45" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A45,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H45" s="19">
         <f>SUM(B45:G45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="19" t="n">
         <v>162</v>
       </c>
-      <c r="B46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G46">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H46">
+      <c r="B46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G46" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A46,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H46" s="19">
         <f>SUM(B46:G46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G47">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H47">
+      <c r="B47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G47" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A47,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H47" s="19">
         <f>SUM(B47:G47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="B48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G48">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H48">
+      <c r="B48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G48" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A48,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H48" s="19">
         <f>SUM(B48:G48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="19" t="n">
         <v>117</v>
       </c>
-      <c r="B49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G49">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H49">
+      <c r="B49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G49" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A49,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H49" s="19">
         <f>SUM(B49:G49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="19" t="n">
         <v>224</v>
       </c>
-      <c r="B50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G50">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H50">
+      <c r="B50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G50" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A50,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H50" s="19">
         <f>SUM(B50:G50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="19" t="n">
         <v>616</v>
       </c>
-      <c r="B51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G51">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H51">
+      <c r="B51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G51" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A51,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H51" s="19">
         <f>SUM(B51:G51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="19" t="n">
         <v>3941</v>
       </c>
-      <c r="B52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G52">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H52">
+      <c r="B52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G52" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A52,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H52" s="19">
         <f>SUM(B52:G52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="B53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G53">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H53">
+      <c r="B53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G53" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A53,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H53" s="19">
         <f>SUM(B53:G53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="19" t="n">
         <v>101</v>
       </c>
-      <c r="B54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G54">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H54">
+      <c r="B54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G54" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A54,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H54" s="19">
         <f>SUM(B54:G54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="19" t="n">
         <v>93</v>
       </c>
-      <c r="B55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G55">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H55">
+      <c r="B55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G55" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A55,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H55" s="19">
         <f>SUM(B55:G55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="19" t="n">
         <v>410</v>
       </c>
-      <c r="B56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H56">
+      <c r="B56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G56" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A56,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H56" s="19">
         <f>SUM(B56:G56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="19" t="n">
         <v>744</v>
       </c>
-      <c r="B57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G57">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H57">
+      <c r="B57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G57" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A57,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H57" s="19">
         <f>SUM(B57:G57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="19" t="n">
         <v>1011</v>
       </c>
-      <c r="B58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G58">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H58">
+      <c r="B58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G58" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A58,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H58" s="19">
         <f>SUM(B58:G58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="B59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G59">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H59">
+      <c r="B59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G59" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A59,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H59" s="19">
         <f>SUM(B59:G59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="19" t="n">
         <v>167</v>
       </c>
-      <c r="B60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H60">
+      <c r="B60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G60" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A60,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H60" s="19">
         <f>SUM(B60:G60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="19" t="n">
         <v>189</v>
       </c>
-      <c r="B61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G61">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H61">
+      <c r="B61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G61" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A61,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H61" s="19">
         <f>SUM(B61:G61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="19" t="n">
         <v>191</v>
       </c>
-      <c r="B62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G62">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H62">
+      <c r="B62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G62" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A62,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H62" s="19">
         <f>SUM(B62:G62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="19" t="n">
         <v>297</v>
       </c>
-      <c r="B63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G63">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H63">
+      <c r="B63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G63" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A63,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H63" s="19">
         <f>SUM(B63:G63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="19" t="n">
         <v>354</v>
       </c>
-      <c r="B64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G64">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H64">
+      <c r="B64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G64" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A64,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H64" s="19">
         <f>SUM(B64:G64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="19" t="n">
         <v>484</v>
       </c>
-      <c r="B65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G65">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H65">
+      <c r="B65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G65" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A65,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H65" s="19">
         <f>SUM(B65:G65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="19" t="n">
         <v>1266</v>
       </c>
-      <c r="B66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G66">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H66">
+      <c r="B66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G66" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A66,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H66" s="19">
         <f>SUM(B66:G66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="19" t="n">
         <v>2485</v>
       </c>
-      <c r="B67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G67">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H67">
+      <c r="B67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G67" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A67,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H67" s="19">
         <f>SUM(B67:G67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="19" t="n">
         <v>8492</v>
       </c>
-      <c r="B68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G68">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H68">
+      <c r="B68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G68" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A68,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H68" s="19">
         <f>SUM(B68:G68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="19" t="n">
         <v>9697</v>
       </c>
-      <c r="B69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G69">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H69">
+      <c r="B69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G69" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A69,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H69" s="19">
         <f>SUM(B69:G69)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>Untypeable</t>
         </is>
       </c>
-      <c r="B70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,B$43)</f>
-        <v/>
-      </c>
-      <c r="C70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,C$43)</f>
-        <v/>
-      </c>
-      <c r="D70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,D$43)</f>
-        <v/>
-      </c>
-      <c r="E70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,E$43)</f>
-        <v/>
-      </c>
-      <c r="F70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,F$43)</f>
-        <v/>
-      </c>
-      <c r="G70">
-        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,G$43)</f>
-        <v/>
-      </c>
-      <c r="H70">
+      <c r="B70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,B$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,C$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,D$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,E$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,F$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G70" s="19">
+        <f>COUNTIFS(Isolates!$Z$2:$Z$128,$A70,Isolates!$O$2:$O$128,G$43,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H70" s="19">
         <f>SUM(B70:G70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Other STs (single genome)</t>
         </is>
       </c>
-      <c r="B71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,B$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(B44:B70)</f>
-        <v/>
-      </c>
-      <c r="C71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,C$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(C44:C70)</f>
-        <v/>
-      </c>
-      <c r="D71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,D$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(D44:D70)</f>
-        <v/>
-      </c>
-      <c r="E71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,E$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(E44:E70)</f>
-        <v/>
-      </c>
-      <c r="F71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,F$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(F44:F70)</f>
-        <v/>
-      </c>
-      <c r="G71">
-        <f>COUNTIFS(Isolates!$O$2:$O$128,G$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(G44:G70)</f>
-        <v/>
-      </c>
-      <c r="H71">
+      <c r="B71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,B$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(B44:B70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,C$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(C44:C70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,D$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(D44:D70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,E$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(E44:E70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,F$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(F44:F70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G71" s="19">
+        <f>COUNTIFS(Isolates!$O$2:$O$128,G$43,Isolates!$Z$2:$Z$128,"&lt;&gt;")-SUM(G44:G70,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H71" s="19">
         <f>SUM(B71:G71)</f>
         <v/>
       </c>
@@ -2960,35 +2970,36 @@
           <t>Total typed or untypeable</t>
         </is>
       </c>
-      <c r="B72">
+      <c r="B72" s="19">
         <f>SUM(B44:B71)</f>
         <v/>
       </c>
-      <c r="C72">
+      <c r="C72" s="19">
         <f>SUM(C44:C71)</f>
         <v/>
       </c>
-      <c r="D72">
+      <c r="D72" s="19">
         <f>SUM(D44:D71)</f>
         <v/>
       </c>
-      <c r="E72">
+      <c r="E72" s="19">
         <f>SUM(E44:E71)</f>
         <v/>
       </c>
-      <c r="F72">
+      <c r="F72" s="19">
         <f>SUM(F44:F71)</f>
         <v/>
       </c>
-      <c r="G72">
+      <c r="G72" s="19">
         <f>SUM(G44:G71)</f>
         <v/>
       </c>
-      <c r="H72">
+      <c r="H72" s="19">
         <f>SUM(H44:H71)</f>
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="37" t="inlineStr">
         <is>
@@ -3039,287 +3050,288 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="B76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G76">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H76">
+      <c r="B76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G76" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncI2*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H76" s="19">
         <f>SUM(B76:G76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="B77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G77">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H77">
+      <c r="B77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G77" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncX4*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H77" s="19">
         <f>SUM(B77:G77)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>IncHI2</t>
         </is>
       </c>
-      <c r="B78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G78">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H78">
+      <c r="B78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G78" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI2*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H78" s="19">
         <f>SUM(B78:G78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>IncHI1</t>
         </is>
       </c>
-      <c r="B79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G79">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H79">
+      <c r="B79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G79" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncHI1*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H79" s="19">
         <f>SUM(B79:G79)</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>IncF (FII/FIB/FIA)</t>
         </is>
       </c>
-      <c r="B80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G80">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H80">
+      <c r="B80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G80" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"*IncF*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H80" s="19">
         <f>SUM(B80:G80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>Other rep cluster (no Inc type)</t>
         </is>
       </c>
-      <c r="B81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G81">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H81">
+      <c r="B81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G81" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"rep_cluster*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H81" s="19">
         <f>SUM(B81:G81)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>Plasmid, no replicon detected</t>
         </is>
       </c>
-      <c r="B82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G82">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H82">
+      <c r="B82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G82" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Plasmid, no replicon*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H82" s="19">
         <f>SUM(B82:G82)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>Chromosomal or unresolved</t>
         </is>
       </c>
-      <c r="B83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,B$75)</f>
-        <v/>
-      </c>
-      <c r="C83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,C$75)</f>
-        <v/>
-      </c>
-      <c r="D83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,D$75)</f>
-        <v/>
-      </c>
-      <c r="E83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,E$75)</f>
-        <v/>
-      </c>
-      <c r="F83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,F$75)</f>
-        <v/>
-      </c>
-      <c r="G83">
-        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,G$75)</f>
-        <v/>
-      </c>
-      <c r="H83">
+      <c r="B83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,B$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,C$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="D83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,D$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="E83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,E$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="F83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,F$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="G83" s="19">
+        <f>COUNTIFS(Isolates!$AA$2:$AA$128,"Chromosomal*",Isolates!$O$2:$O$128,G$75,Isolates!$AG$2:$AG$128,"Yes")</f>
+        <v/>
+      </c>
+      <c r="H83" s="19">
         <f>SUM(B83:G83)</f>
         <v/>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>Note: ST and replicon columns were filled from the Galaxy_results sheet. Rows beyond genome 118 were added by the corrected retrieval in v2 and typed in the Galaxy history "mcr Africa D typing".</t>
         </is>
@@ -3336,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF128"/>
+  <dimension ref="A1:AH128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="19" min="1" max="2"/>
@@ -3528,6 +3540,16 @@
           <t>IS30-family element on mcr contig</t>
         </is>
       </c>
+      <c r="AG1" s="37" t="inlineStr">
+        <is>
+          <t>Included in analysis</t>
+        </is>
+      </c>
+      <c r="AH1" s="37" t="inlineStr">
+        <is>
+          <t>Reason for exclusion</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="20">
       <c r="A2" s="25" t="inlineStr">
@@ -3632,6 +3654,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG2" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="20">
       <c r="A3" s="25" t="inlineStr">
@@ -3750,6 +3777,11 @@
       <c r="AF3" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG3" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3870,6 +3902,11 @@
       <c r="AF4" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG4" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3988,6 +4025,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG5" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="20">
       <c r="A6" s="25" t="inlineStr">
@@ -4104,6 +4146,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG6" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="20">
       <c r="A7" s="25" t="inlineStr">
@@ -4222,6 +4269,11 @@
       <c r="AF7" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG7" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4346,6 +4398,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG8" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="20">
       <c r="A9" s="25" t="inlineStr">
@@ -4462,6 +4519,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG9" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="20">
       <c r="A10" s="25" t="inlineStr">
@@ -4582,6 +4644,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG10" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="20">
       <c r="A11" s="25" t="inlineStr">
@@ -4706,6 +4773,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG11" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="20">
       <c r="A12" s="25" t="inlineStr">
@@ -4830,6 +4902,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG12" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="20">
       <c r="A13" s="25" t="inlineStr">
@@ -4954,6 +5031,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG13" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="20">
       <c r="A14" s="25" t="inlineStr">
@@ -5078,6 +5160,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG14" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="20">
       <c r="A15" s="25" t="inlineStr">
@@ -5194,6 +5281,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG15" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="20">
       <c r="A16" s="25" t="inlineStr">
@@ -5316,6 +5408,11 @@
       <c r="AF16" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG16" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5444,6 +5541,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG17" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="20">
       <c r="A18" s="25" t="inlineStr">
@@ -5558,6 +5660,11 @@
       <c r="AF18" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG18" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5664,6 +5771,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG19" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="20">
       <c r="A20" s="25" t="inlineStr">
@@ -5780,6 +5892,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG20" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="20">
       <c r="A21" s="25" t="inlineStr">
@@ -5896,6 +6013,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG21" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="20">
       <c r="A22" s="25" t="inlineStr">
@@ -6014,6 +6136,11 @@
       <c r="AF22" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG22" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6132,6 +6259,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG23" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="20">
       <c r="A24" s="25" t="inlineStr">
@@ -6248,6 +6380,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG24" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="20">
       <c r="A25" s="25" t="inlineStr">
@@ -6364,6 +6501,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG25" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="20">
       <c r="A26" s="25" t="inlineStr">
@@ -6484,6 +6626,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG26" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="20">
       <c r="A27" s="25" t="inlineStr">
@@ -6604,6 +6751,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG27" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="20">
       <c r="A28" s="25" t="inlineStr">
@@ -6718,6 +6870,11 @@
       <c r="AF28" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG28" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6840,6 +6997,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG29" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="20">
       <c r="A30" s="25" t="inlineStr">
@@ -6960,6 +7122,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG30" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="20">
       <c r="A31" s="25" t="inlineStr">
@@ -7080,6 +7247,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG31" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="20">
       <c r="A32" s="25" t="inlineStr">
@@ -7200,6 +7372,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG32" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="20">
       <c r="A33" s="25" t="inlineStr">
@@ -7320,6 +7497,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG33" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="20">
       <c r="A34" s="25" t="inlineStr">
@@ -7440,6 +7622,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG34" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="20">
       <c r="A35" s="25" t="inlineStr">
@@ -7560,6 +7747,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG35" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="20">
       <c r="A36" s="25" t="inlineStr">
@@ -7680,6 +7872,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG36" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="20">
       <c r="A37" s="25" t="inlineStr">
@@ -7800,6 +7997,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG37" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="20">
       <c r="A38" s="25" t="inlineStr">
@@ -7920,6 +8122,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG38" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="20">
       <c r="A39" s="25" t="inlineStr">
@@ -8040,6 +8247,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG39" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="20">
       <c r="A40" s="25" t="inlineStr">
@@ -8166,6 +8378,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG40" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="20">
       <c r="A41" s="25" t="inlineStr">
@@ -8286,6 +8503,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG41" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="20">
       <c r="A42" s="25" t="inlineStr">
@@ -8406,6 +8628,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG42" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="20">
       <c r="A43" s="25" t="inlineStr">
@@ -8526,6 +8753,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG43" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="20">
       <c r="A44" s="25" t="inlineStr">
@@ -8646,6 +8878,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG44" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="20">
       <c r="A45" s="25" t="inlineStr">
@@ -8766,6 +9003,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG45" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="20">
       <c r="A46" s="25" t="inlineStr">
@@ -8886,6 +9128,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG46" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="20">
       <c r="A47" s="25" t="inlineStr">
@@ -9006,6 +9253,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG47" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="20">
       <c r="A48" s="25" t="inlineStr">
@@ -9126,6 +9378,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG48" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="20">
       <c r="A49" s="25" t="inlineStr">
@@ -9246,6 +9503,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG49" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="20">
       <c r="A50" s="25" t="inlineStr">
@@ -9366,6 +9628,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG50" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="20">
       <c r="A51" s="25" t="inlineStr">
@@ -9486,6 +9753,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG51" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="20">
       <c r="A52" s="25" t="inlineStr">
@@ -9606,6 +9878,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG52" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="20">
       <c r="A53" s="25" t="inlineStr">
@@ -9732,6 +10009,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG53" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="20">
       <c r="A54" s="25" t="inlineStr">
@@ -9852,6 +10134,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG54" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="20">
       <c r="A55" s="25" t="inlineStr">
@@ -9972,6 +10259,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG55" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="20">
       <c r="A56" s="25" t="inlineStr">
@@ -10092,6 +10384,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG56" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="20">
       <c r="A57" s="25" t="inlineStr">
@@ -10212,6 +10509,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG57" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="20">
       <c r="A58" s="25" t="inlineStr">
@@ -10332,6 +10634,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG58" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="20">
       <c r="A59" s="25" t="inlineStr">
@@ -10452,6 +10759,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG59" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="20">
       <c r="A60" s="25" t="inlineStr">
@@ -10572,6 +10884,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG60" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="20">
       <c r="A61" s="25" t="inlineStr">
@@ -10692,6 +11009,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG61" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="20">
       <c r="A62" s="25" t="inlineStr">
@@ -10812,6 +11134,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG62" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="20">
       <c r="A63" s="25" t="inlineStr">
@@ -10932,6 +11259,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG63" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="20">
       <c r="A64" s="25" t="inlineStr">
@@ -11052,6 +11384,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG64" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="20">
       <c r="A65" s="25" t="inlineStr">
@@ -11172,6 +11509,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG65" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="20">
       <c r="A66" s="25" t="inlineStr">
@@ -11292,6 +11634,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG66" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="20">
       <c r="A67" s="25" t="inlineStr">
@@ -11412,6 +11759,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG67" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="20">
       <c r="A68" s="25" t="inlineStr">
@@ -11532,6 +11884,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG68" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="20">
       <c r="A69" s="25" t="inlineStr">
@@ -11652,6 +12009,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG69" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="20">
       <c r="A70" s="25" t="inlineStr">
@@ -11752,6 +12114,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG70" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="20">
       <c r="A71" s="25" t="inlineStr">
@@ -11856,6 +12223,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG71" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="20">
       <c r="A72" s="25" t="inlineStr">
@@ -11992,6 +12364,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG72" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="20">
       <c r="A73" s="25" t="inlineStr">
@@ -12122,6 +12499,11 @@
       <c r="AF73" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG73" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12248,6 +12630,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG74" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="20">
       <c r="A75" s="25" t="inlineStr">
@@ -12364,6 +12751,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG75" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="20">
       <c r="A76" s="25" t="inlineStr">
@@ -12482,6 +12874,11 @@
       <c r="AF76" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG76" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12600,6 +12997,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG77" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="20">
       <c r="A78" s="25" t="inlineStr">
@@ -12714,6 +13116,11 @@
       <c r="AF78" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG78" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -12836,6 +13243,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG79" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="20">
       <c r="A80" s="25" t="inlineStr">
@@ -12948,6 +13360,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG80" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="20">
       <c r="A81" s="25" t="inlineStr">
@@ -13068,6 +13485,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG81" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="20">
       <c r="A82" s="25" t="inlineStr">
@@ -13186,6 +13608,11 @@
       <c r="AF82" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG82" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -13310,6 +13737,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG83" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="20">
       <c r="A84" s="25" t="inlineStr">
@@ -13436,6 +13868,11 @@
       <c r="AF84" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG84" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -13554,6 +13991,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG85" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="20">
       <c r="A86" s="25" t="inlineStr">
@@ -13670,6 +14112,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG86" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="20">
       <c r="A87" s="25" t="inlineStr">
@@ -13794,6 +14241,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG87" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="20">
       <c r="A88" s="25" t="inlineStr">
@@ -13910,6 +14362,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG88" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="20">
       <c r="A89" s="25" t="inlineStr">
@@ -14038,6 +14495,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG89" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="20">
       <c r="A90" s="25" t="inlineStr">
@@ -14164,6 +14626,11 @@
       <c r="AF90" s="19" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AG90" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -14290,6 +14757,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG91" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="20">
       <c r="A92" s="25" t="inlineStr">
@@ -14418,6 +14890,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG92" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="20">
       <c r="A93" s="25" t="inlineStr">
@@ -14544,6 +15021,11 @@
       <c r="AF93" s="19" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="AG93" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -14666,6 +15148,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG94" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="20">
       <c r="A95" s="25" t="inlineStr">
@@ -14786,6 +15273,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG95" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="20">
       <c r="A96" s="25" t="inlineStr">
@@ -14906,6 +15398,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG96" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="20">
       <c r="A97" s="25" t="inlineStr">
@@ -15026,6 +15523,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG97" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="20">
       <c r="A98" s="25" t="inlineStr">
@@ -15146,6 +15648,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG98" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="20">
       <c r="A99" s="25" t="inlineStr">
@@ -15266,6 +15773,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG99" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="20">
       <c r="A100" s="25" t="inlineStr">
@@ -15386,6 +15898,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG100" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="20">
       <c r="A101" s="25" t="inlineStr">
@@ -15506,6 +16023,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG101" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="20">
       <c r="A102" s="25" t="inlineStr">
@@ -15626,6 +16148,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG102" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="20">
       <c r="A103" s="25" t="inlineStr">
@@ -15742,6 +16269,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG103" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="20">
       <c r="A104" s="25" t="inlineStr">
@@ -15858,6 +16390,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG104" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="20">
       <c r="A105" s="25" t="inlineStr">
@@ -15974,6 +16511,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG105" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="20">
       <c r="A106" s="25" t="inlineStr">
@@ -16090,6 +16632,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG106" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="20">
       <c r="A107" s="25" t="inlineStr">
@@ -16210,6 +16757,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG107" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="20">
       <c r="A108" s="25" t="inlineStr">
@@ -16330,6 +16882,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG108" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="20">
       <c r="A109" s="25" t="inlineStr">
@@ -16452,6 +17009,11 @@
       <c r="AF109" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG109" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -16570,6 +17132,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG110" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="20">
       <c r="A111" s="25" t="inlineStr">
@@ -16686,6 +17253,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG111" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="20">
       <c r="A112" s="25" t="inlineStr">
@@ -16802,6 +17374,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG112" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="20">
       <c r="A113" s="25" t="inlineStr">
@@ -16918,6 +17495,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG113" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="20">
       <c r="A114" s="25" t="inlineStr">
@@ -17034,6 +17616,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG114" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="20">
       <c r="A115" s="25" t="inlineStr">
@@ -17150,6 +17737,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG115" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="20">
       <c r="A116" s="25" t="inlineStr">
@@ -17261,6 +17853,11 @@
       <c r="AE116" s="19" t="n">
         <v>0.51</v>
       </c>
+      <c r="AG116" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="20">
       <c r="A117" s="25" t="inlineStr">
@@ -17379,6 +17976,11 @@
       <c r="AF117" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG117" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -17501,6 +18103,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AG118" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="20">
       <c r="A119" s="25" t="inlineStr">
@@ -17617,952 +18224,1007 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="AG119" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="19" t="inlineStr">
         <is>
           <t>PDT003089299.1</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="19" t="inlineStr">
         <is>
           <t>SAMEA120683848</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>PRJEB104706</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="19" t="inlineStr">
         <is>
           <t>GCA_977857845.1</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" s="19" t="inlineStr">
         <is>
           <t>Central African Republic</t>
         </is>
       </c>
-      <c r="K120" t="n">
+      <c r="K120" s="19" t="n">
         <v>2022</v>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="L120" s="19" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="M120" s="19" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="O120" s="19" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
+      <c r="Q120" s="19" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
+      <c r="R120" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T120" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-55</t>
         </is>
       </c>
-      <c r="X120" t="n">
+      <c r="X120" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Y120" s="19" t="inlineStr">
         <is>
           <t>aadA1 aadA2 aph(3')-Ia blaCTX-M-55 cmlA1 dfrA12 gyrA_D87N gyrA_S83L mcr-1.1 parC_S80I qnrS13 sul3 tet(A) tet(M)</t>
         </is>
       </c>
-      <c r="Z120" t="n">
+      <c r="Z120" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="AA120" t="inlineStr">
+      <c r="AA120" s="19" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
+      <c r="AB120" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). mcr-1.1 and IncX4 on the same 32.7 kb contig.</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
+      <c r="AC120" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD120" t="n">
+      <c r="AD120" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE120" t="n">
+      <c r="AE120" s="19" t="n">
         <v>0.22</v>
       </c>
-      <c r="AF120" t="inlineStr">
+      <c r="AF120" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG120" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="19" t="inlineStr">
         <is>
           <t>PDT003089301.1</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t>SAMEA120683850</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>PRJEB104706</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="19" t="inlineStr">
         <is>
           <t>GCA_977859995.1</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" s="19" t="inlineStr">
         <is>
           <t>Central African Republic</t>
         </is>
       </c>
-      <c r="K121" t="n">
+      <c r="K121" s="19" t="n">
         <v>2022</v>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L121" s="19" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="M121" s="19" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="O121" s="19" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
+      <c r="Q121" s="19" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
+      <c r="R121" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T121" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-55</t>
         </is>
       </c>
-      <c r="X121" t="n">
+      <c r="X121" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Y121" s="19" t="inlineStr">
         <is>
           <t>aadA1 aadA2 aph(3'')-Ib aph(3')-Ia aph(6)-Id blaCTX-M-55 cmlA1 dfrA12 erm(B) gyrA_D87N gyrA_S83L mcr-1.1 mph(A) parC_S80I qnrS13 sul1 sul2 sul3 tet(A) tet(B) tet(M)</t>
         </is>
       </c>
-      <c r="Z121" t="n">
+      <c r="Z121" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="AA121" t="inlineStr">
+      <c r="AA121" s="19" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
+      <c r="AB121" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Same ST and replicon as SAMEA120683848, same submission.</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
+      <c r="AC121" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD121" t="n">
+      <c r="AD121" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE121" t="n">
+      <c r="AE121" s="19" t="n">
         <v>0.68</v>
       </c>
-      <c r="AF121" t="inlineStr">
+      <c r="AF121" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG121" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="19" t="inlineStr">
         <is>
           <t>PDT000640376.1</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="19" t="inlineStr">
         <is>
           <t>SAMEA5988742</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="19" t="inlineStr">
         <is>
           <t>PRJEB34702</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="19" t="inlineStr">
         <is>
           <t>GCA_902703155.1</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122" s="19" t="inlineStr">
         <is>
           <t>Eco04570</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K122" t="n">
+      <c r="K122" s="19" t="n">
         <v>2016</v>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L122" s="19" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
+      <c r="M122" s="19" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
+      <c r="N122" s="19" t="inlineStr">
         <is>
           <t>clinical material</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="O122" s="19" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
+      <c r="Q122" s="19" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="X122" t="n">
+      <c r="R122" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X122" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Y122" s="19" t="inlineStr">
         <is>
           <t>aph(3'')-Ib=PARTIAL_END_OF_CONTIG aph(6)-Id bleO dfrA14 gyrA_S83L mcr-1.1 oqxA oqxB sul2 tet(B)</t>
         </is>
       </c>
-      <c r="Z122" t="n">
+      <c r="Z122" s="19" t="n">
         <v>602</v>
       </c>
-      <c r="AA122" t="inlineStr">
+      <c r="AA122" s="19" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
+      <c r="AB122" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). mcr-1.1 and IncI2 on the same 56.2 kb contig.</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
+      <c r="AC122" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD122" t="n">
+      <c r="AD122" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE122" t="n">
+      <c r="AE122" s="19" t="n">
         <v>0.16</v>
       </c>
-      <c r="AF122" t="inlineStr">
+      <c r="AF122" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG122" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="19" t="inlineStr">
         <is>
           <t>PDT000409988.1</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="19" t="inlineStr">
         <is>
           <t>SAMN09303237</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="19" t="inlineStr">
         <is>
           <t>PRJNA412434</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="19" t="inlineStr">
         <is>
           <t>GCA_003795445.1</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G123" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" s="19" t="inlineStr">
         <is>
           <t>PN256E8</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K123" t="n">
+      <c r="K123" s="19" t="n">
         <v>2016</v>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L123" s="19" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="M123" s="19" t="inlineStr">
         <is>
           <t>pig</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
+      <c r="N123" s="19" t="inlineStr">
         <is>
           <t>nares</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O123" s="19" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr">
+      <c r="Q123" s="19" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
+      <c r="R123" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="T123" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-55</t>
         </is>
       </c>
-      <c r="X123" t="n">
+      <c r="X123" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Y123" s="19" t="inlineStr">
         <is>
           <t>aac(6')-Ib3 aadA5 aph(6)-Id=PARTIAL_END_OF_CONTIG blaCTX-M-55 blaTEM=PARTIAL bleO dfrA17 floR fosA3 mcr-1.1 oqxA oqxB sul2 tet(A)</t>
         </is>
       </c>
-      <c r="Z123" t="n">
+      <c r="Z123" s="19" t="n">
         <v>9440</v>
       </c>
-      <c r="AA123" t="inlineStr">
+      <c r="AA123" s="19" t="inlineStr">
         <is>
           <t>IncHI2A (MOB-Recon bin)</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
+      <c r="AB123" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Pig nasal isolate; mcr contig 2.9 kb, IncHI2 from MOB-Recon bin only.</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
+      <c r="AC123" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD123" t="n">
+      <c r="AD123" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE123" t="n">
+      <c r="AE123" s="19" t="n">
         <v>0.47</v>
       </c>
-      <c r="AF123" t="inlineStr">
+      <c r="AF123" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG123" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>PDT000878268.1</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t>SAMN14219481</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="19" t="inlineStr">
         <is>
           <t>PRJNA609073</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="19" t="inlineStr">
         <is>
           <t>GCA_015208565.1</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G124" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" s="19" t="inlineStr">
         <is>
           <t>D96_9</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K124" t="n">
+      <c r="K124" s="19" t="n">
         <v>2018</v>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L124" s="19" t="inlineStr">
         <is>
           <t>2018-09-11</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N124" s="19" t="inlineStr">
         <is>
           <t>wastewater</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="O124" s="19" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="Q124" s="19" t="inlineStr">
         <is>
           <t>environmental/other</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="R124" s="19" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="X124" t="n">
+      <c r="X124" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Y124" s="19" t="inlineStr">
         <is>
           <t>blaTEM-1 cyaA_S352T mcr-9=PARTIAL_END_OF_CONTIG tet(A)</t>
         </is>
       </c>
-      <c r="Z124" t="n">
+      <c r="Z124" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AA124" s="19" t="inlineStr">
         <is>
           <t>Chromosomal or unresolved (MOB-Recon)</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
+      <c r="AB124" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Wastewater mcr-9 on a 2.6 kb contig placed in the chromosome bin; unresolved.</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
+      <c r="AC124" s="19" t="inlineStr">
         <is>
           <t>|mcr-9|</t>
         </is>
       </c>
-      <c r="AD124" t="n">
+      <c r="AD124" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE124" t="n">
+      <c r="AE124" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="AF124" t="inlineStr">
+      <c r="AF124" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG124" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AH124" s="19" t="inlineStr">
+        <is>
+          <t>CheckM2 contamination 6.00%, above the 5% ceiling stated in the Methods</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>PDT001428169.1</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t>SAMN28613555</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="19" t="inlineStr">
         <is>
           <t>PRJNA841695</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="19" t="inlineStr">
         <is>
           <t>GCA_025336805.1</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G125" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" s="19" t="inlineStr">
         <is>
           <t>Q0169</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" s="19" t="inlineStr">
         <is>
           <t>Democratic Republic of the Congo</t>
         </is>
       </c>
-      <c r="K125" t="n">
+      <c r="K125" s="19" t="n">
         <v>2017</v>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="L125" s="19" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M125" s="19" t="inlineStr">
         <is>
           <t>Papio cynocephalus</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
+      <c r="N125" s="19" t="inlineStr">
         <is>
           <t>fecal samples</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O125" s="19" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="X125" t="n">
+      <c r="R125" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X125" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Y125" s="19" t="inlineStr">
         <is>
           <t>blaTEM-1 cyaA_S352T mcr-1.1</t>
         </is>
       </c>
-      <c r="Z125" t="n">
+      <c r="Z125" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="AA125" t="inlineStr">
+      <c r="AA125" s="19" t="inlineStr">
         <is>
           <t>Plasmid, no replicon detected (MOB-Recon)</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
+      <c r="AB125" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Wild baboon faeces; 2.5 kb mcr contig in a plasmid bin with no typeable replicon.</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
+      <c r="AC125" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD125" t="n">
+      <c r="AD125" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE125" t="n">
+      <c r="AE125" s="19" t="n">
         <v>0.09</v>
       </c>
-      <c r="AF125" t="inlineStr">
+      <c r="AF125" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG125" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>PDT001428170.1</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>SAMN28613556</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="19" t="inlineStr">
         <is>
           <t>PRJNA841695</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="19" t="inlineStr">
         <is>
           <t>GCA_025336825.1</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G126" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126" s="19" t="inlineStr">
         <is>
           <t>Q0170</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" s="19" t="inlineStr">
         <is>
           <t>Democratic Republic of the Congo</t>
         </is>
       </c>
-      <c r="K126" t="n">
+      <c r="K126" s="19" t="n">
         <v>2017</v>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="L126" s="19" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
+      <c r="M126" s="19" t="inlineStr">
         <is>
           <t>Papio cynocephalus</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
+      <c r="N126" s="19" t="inlineStr">
         <is>
           <t>fecal samples</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O126" s="19" t="inlineStr">
         <is>
           <t>Other animal</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="X126" t="n">
+      <c r="R126" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="X126" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Y126" s="19" t="inlineStr">
         <is>
           <t>aadA1 aph(3'')-Ib aph(6)-Id blaTEM-1 catA1 cirA_N81TerfsTer0 dfrA1 gyrA_S83L mcr-1.1 mph(B) rdmCL sul1 sul2 tet(A)</t>
         </is>
       </c>
-      <c r="Z126" t="n">
+      <c r="Z126" s="19" t="n">
         <v>101</v>
       </c>
-      <c r="AA126" t="inlineStr">
+      <c r="AA126" s="19" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
+      <c r="AB126" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Wild baboon faeces; mcr-1.1 and IncI2 on the same 66.5 kb contig.</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
+      <c r="AC126" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD126" t="n">
+      <c r="AD126" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE126" t="n">
+      <c r="AE126" s="19" t="n">
         <v>0.76</v>
       </c>
-      <c r="AF126" t="inlineStr">
+      <c r="AF126" s="19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="AG126" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="19" t="inlineStr">
         <is>
           <t>PDT002034360.1</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="19" t="inlineStr">
         <is>
           <t>SAMN36943049</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="19" t="inlineStr">
         <is>
           <t>PRJNA999080</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="19" t="inlineStr">
         <is>
           <t>GCA_034465125.1</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="19" t="inlineStr">
         <is>
           <t>SRR25608269</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G127" s="19" t="inlineStr">
         <is>
           <t>Short-read assembly (Shovill)</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" s="19" t="inlineStr">
         <is>
           <t>R2745-Af49</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K127" t="n">
+      <c r="K127" s="19" t="n">
         <v>2015</v>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="L127" s="19" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M127" s="19" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O127" s="19" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
+      <c r="Q127" s="19" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
+      <c r="R127" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="S127" s="19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T127" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-55</t>
         </is>
       </c>
-      <c r="X127" t="n">
+      <c r="X127" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Y127" s="19" t="inlineStr">
         <is>
           <t>aac(6')-Ib3 aadA1 blaCTX-M-55 blaTEM=PARTIAL blaTEM=PARTIAL_END_OF_CONTIG cirA_D84IfsTer16 dfrA15 floR fosA3 gyrA_D87N gyrA_S83L mcr-1.1 parC_S80I sul1 sul2 tet(A) tet(A)=PARTIAL_END_OF_CONTIG</t>
         </is>
       </c>
-      <c r="Z127" t="n">
+      <c r="Z127" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="AA127" t="inlineStr">
+      <c r="AA127" s="19" t="inlineStr">
         <is>
           <t>IncHI2A/IncFIB (MOB-Recon bin, mixed replicons)</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
+      <c r="AB127" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Two mcr-1.1 calls on 2.6 kb and 2.7 kb contigs, one chromosome-binned and one in a mixed IncFIB/IncHI2A bin; counted once as unresolved.</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
+      <c r="AC127" s="19" t="inlineStr">
         <is>
           <t>|mcr-1.1|</t>
         </is>
       </c>
-      <c r="AD127" t="n">
+      <c r="AD127" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE127" t="n">
+      <c r="AE127" s="19" t="n">
         <v>1.43</v>
       </c>
-      <c r="AF127" t="inlineStr">
+      <c r="AF127" s="19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="AG127" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>PDT003000705.1</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t>SAMN49772998</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>PRJNA642017</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="19" t="inlineStr">
         <is>
           <t>GCA_053709775.1</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G128" s="19" t="inlineStr">
         <is>
           <t>GenBank assembly (no reads)</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="19" t="inlineStr">
         <is>
           <t>UPMP1740</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="K128" s="19" t="n">
         <v>2019</v>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L128" s="19" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="N128" s="19" t="inlineStr">
         <is>
           <t>cucumber</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O128" s="19" t="inlineStr">
         <is>
           <t>Food (non-poultry)</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="T128" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-14</t>
         </is>
       </c>
-      <c r="X128" t="n">
+      <c r="X128" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Y128" s="19" t="inlineStr">
         <is>
           <t>blaCTX-M-14 fosA3 mcr-9.1</t>
         </is>
       </c>
-      <c r="Z128" t="n">
+      <c r="Z128" s="19" t="n">
         <v>297</v>
       </c>
-      <c r="AA128" t="inlineStr">
+      <c r="AA128" s="19" t="inlineStr">
         <is>
           <t>Chromosomal or unresolved (MOB-Recon)</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
+      <c r="AB128" s="19" t="inlineStr">
         <is>
           <t>Added by the corrected retrieval (v2). Cucumber isolate; mcr-9.1 on a 3.5 kb contig placed in the chromosome bin; unresolved.</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
+      <c r="AC128" s="19" t="inlineStr">
         <is>
           <t>|mcr-9.1|</t>
         </is>
       </c>
-      <c r="AD128" t="n">
+      <c r="AD128" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="AE128" t="n">
+      <c r="AE128" s="19" t="n">
         <v>3.64</v>
       </c>
-      <c r="AF128" t="inlineStr">
+      <c r="AF128" s="19" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AG128" s="19" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -20484,42 +21146,42 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>SRR25608269</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>SAMN36943049</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>ILLUMINA</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>PAIRED</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
         <is>
           <t>Short-read assembly (Shovill)</t>
         </is>
@@ -33445,934 +34107,934 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="19" t="inlineStr">
         <is>
           <t>SAMEA120683848</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="19" t="inlineStr">
         <is>
           <t>GCA_977857845.1</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="19" t="n">
         <v>127</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" s="19" t="n">
         <v>4775047</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="19" t="n">
         <v>94422</v>
       </c>
-      <c r="I120" t="n">
+      <c r="I120" s="19" t="n">
         <v>50.54</v>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
+      <c r="K120" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L120" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M120" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
+      <c r="N120" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="O120" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="P120" s="19" t="inlineStr">
         <is>
           <t>CDWHFB010000042.1</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
+      <c r="Q120" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R120" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
+      <c r="S120" s="19" t="inlineStr">
         <is>
           <t>IncX4_1</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="T120" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="U120" s="19" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
+      <c r="V120" s="19" t="inlineStr">
         <is>
           <t>MOBP</t>
         </is>
       </c>
-      <c r="W120" t="n">
+      <c r="W120" s="19" t="n">
         <v>32730</v>
       </c>
-      <c r="X120" t="n">
+      <c r="X120" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Y120" s="19" t="inlineStr">
         <is>
           <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
+      <c r="Z120" s="19" t="inlineStr">
         <is>
           <t>ColpVC_1, IncFII_1, IncX1_1, IncX4_1, p0111_1</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="19" t="inlineStr">
         <is>
           <t>SAMEA120683850</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t>GCA_977859995.1</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" s="19" t="n">
         <v>5508014</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" s="19" t="n">
         <v>72378</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I121" s="19" t="n">
         <v>50.35</v>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
+      <c r="K121" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L121" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M121" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
+      <c r="N121" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="O121" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="P121" s="19" t="inlineStr">
         <is>
           <t>CDWHOZ010000048.1</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
+      <c r="Q121" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R121" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="S121" s="19" t="inlineStr">
         <is>
           <t>IncX4_1</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="T121" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="U121" s="19" t="inlineStr">
         <is>
           <t>IncX4</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr">
+      <c r="V121" s="19" t="inlineStr">
         <is>
           <t>MOBP</t>
         </is>
       </c>
-      <c r="W121" t="n">
+      <c r="W121" s="19" t="n">
         <v>32686</v>
       </c>
-      <c r="X121" t="n">
+      <c r="X121" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Y121" s="19" t="inlineStr">
         <is>
           <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
+      <c r="Z121" s="19" t="inlineStr">
         <is>
           <t>Col(BS512)_1, ColpVC_1, IncFIA_1, IncFIB(AP001918)_1, IncFII_1, IncX1_1, IncX4_1, p0111_1</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="19" t="inlineStr">
         <is>
           <t>SAMEA5988742</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="19" t="inlineStr">
         <is>
           <t>GCA_902703155.1</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="19" t="n">
         <v>107</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" s="19" t="n">
         <v>5289460</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H122" s="19" t="n">
         <v>204049</v>
       </c>
-      <c r="I122" t="n">
+      <c r="I122" s="19" t="n">
         <v>50.53</v>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
+      <c r="K122" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L122" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M122" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
+      <c r="N122" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="O122" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="P122" s="19" t="inlineStr">
         <is>
           <t>CACRYI010000026.1</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
+      <c r="Q122" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R122" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
+      <c r="S122" s="19" t="inlineStr">
         <is>
           <t>IncI2_1_Delta</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="T122" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="U122" s="19" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
+      <c r="V122" s="19" t="inlineStr">
         <is>
           <t>MOBP</t>
         </is>
       </c>
-      <c r="W122" t="n">
+      <c r="W122" s="19" t="n">
         <v>62892</v>
       </c>
-      <c r="X122" t="n">
+      <c r="X122" s="19" t="n">
         <v>602</v>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Y122" s="19" t="inlineStr">
         <is>
           <t>adk(6) fumC(19) gyrB(33) icd(26) mdh(11) purA(8) recA(6)</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
+      <c r="Z122" s="19" t="inlineStr">
         <is>
           <t>IncFIB(AP001918)_1, IncI1_1_Alpha, IncI2_1_Delta</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="19" t="inlineStr">
         <is>
           <t>SAMN09303237</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="19" t="inlineStr">
         <is>
           <t>GCA_003795445.1</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="19" t="n">
         <v>242</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123" s="19" t="n">
         <v>4988197</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H123" s="19" t="n">
         <v>85550</v>
       </c>
-      <c r="I123" t="n">
+      <c r="I123" s="19" t="n">
         <v>50.55</v>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
+      <c r="K123" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L123" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M123" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
+      <c r="N123" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O123" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="P123" s="19" t="inlineStr">
         <is>
           <t>QJRZ01000018.1</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr">
+      <c r="Q123" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R123" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="T123" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="U123" s="19" t="inlineStr">
         <is>
           <t>IncHI2A, rep_cluster_1088</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
+      <c r="V123" s="19" t="inlineStr">
         <is>
           <t>MOBH</t>
         </is>
       </c>
-      <c r="W123" t="n">
+      <c r="W123" s="19" t="n">
         <v>250002</v>
       </c>
-      <c r="X123" t="n">
+      <c r="X123" s="19" t="n">
         <v>9440</v>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Y123" s="19" t="inlineStr">
         <is>
           <t>adk(10) fumC(11) gyrB(4) icd(8) mdh(8) purA(724) recA(2)</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
+      <c r="Z123" s="19" t="inlineStr">
         <is>
           <t>IncHI2A_1, IncHI2_1, IncN_1</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>SAMN14219481</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t>GCA_015208565.1</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="19" t="n">
         <v>216</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124" s="19" t="n">
         <v>5321899</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H124" s="19" t="n">
         <v>249887</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I124" s="19" t="n">
         <v>50.8</v>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="19" t="inlineStr">
         <is>
           <t>FAIL CheckM2 contamination 6.00% (&gt;5% threshold)</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K124" s="19" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L124" s="19" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M124" s="19" t="inlineStr">
         <is>
           <t>BLASTX</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N124" s="19" t="inlineStr">
         <is>
           <t>99.74</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="O124" s="19" t="inlineStr">
         <is>
           <t>99.21</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="P124" s="19" t="inlineStr">
         <is>
           <t>JAAOAA010000190.1</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="Q124" s="19" t="inlineStr">
         <is>
           <t>mcr-9</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="R124" s="19" t="inlineStr">
         <is>
           <t>mcr-9_1</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="T124" s="19" t="inlineStr">
         <is>
           <t>chromosome</t>
         </is>
       </c>
-      <c r="X124" t="n">
+      <c r="X124" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Y124" s="19" t="inlineStr">
         <is>
           <t>adk(21) fumC(35) gyrB(27) icd(6) mdh(5) purA(5) recA(4)</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="Z124" s="19" t="inlineStr">
         <is>
           <t>IncFIA_1, IncFIB(AP001918)_1, IncFIC(FII)_1</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>SAMN28613555</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t>GCA_025336805.1</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="19" t="n">
         <v>343</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125" s="19" t="n">
         <v>5278367</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H125" s="19" t="n">
         <v>155237</v>
       </c>
-      <c r="I125" t="n">
+      <c r="I125" s="19" t="n">
         <v>50.53</v>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
+      <c r="K125" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M125" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr">
+      <c r="N125" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O125" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="P125" s="19" t="inlineStr">
         <is>
           <t>JAODFU010000074.1</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr">
+      <c r="Q125" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R125" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="T125" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="W125" t="n">
+      <c r="W125" s="19" t="n">
         <v>27806</v>
       </c>
-      <c r="X125" t="n">
+      <c r="X125" s="19" t="n">
         <v>69</v>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Y125" s="19" t="inlineStr">
         <is>
           <t>adk(21) fumC(35) gyrB(27) icd(6) mdh(5) purA(5) recA(4)</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
+      <c r="Z125" s="19" t="inlineStr">
         <is>
           <t>Col156_1, IncFII(29)_1, IncFII(pAMA1167-NDM-5)_1</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>SAMN28613556</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>GCA_025336825.1</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="19" t="n">
         <v>49</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126" s="19" t="n">
         <v>5069550</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H126" s="19" t="n">
         <v>354723</v>
       </c>
-      <c r="I126" t="n">
+      <c r="I126" s="19" t="n">
         <v>50.44</v>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
+      <c r="K126" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L126" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M126" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr">
+      <c r="N126" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O126" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P126" s="19" t="inlineStr">
         <is>
           <t>JAODFT010000018.1</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
+      <c r="Q126" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R126" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
+      <c r="S126" s="19" t="inlineStr">
         <is>
           <t>IncI2_1_Delta</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="T126" s="19" t="inlineStr">
         <is>
           <t>plasmid</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="U126" s="19" t="inlineStr">
         <is>
           <t>IncI2</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr">
+      <c r="V126" s="19" t="inlineStr">
         <is>
           <t>MOBP</t>
         </is>
       </c>
-      <c r="W126" t="n">
+      <c r="W126" s="19" t="n">
         <v>68367</v>
       </c>
-      <c r="X126" t="n">
+      <c r="X126" s="19" t="n">
         <v>101</v>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Y126" s="19" t="inlineStr">
         <is>
           <t>adk(43) fumC(41) gyrB(15) icd(18) mdh(11) purA(7) recA(6)</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
+      <c r="Z126" s="19" t="inlineStr">
         <is>
           <t>IncFIB(AP001918)_1, IncI2_1_Delta, IncQ1_1</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="19" t="inlineStr">
         <is>
           <t>SAMN36943049</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="19" t="inlineStr">
         <is>
           <t>GCA_034465125.1</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="19" t="inlineStr">
         <is>
           <t>A (SRA reads)</t>
         </is>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="19" t="n">
         <v>214</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" s="19" t="n">
         <v>5295826</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127" s="19" t="n">
         <v>83445</v>
       </c>
-      <c r="I127" t="n">
+      <c r="I127" s="19" t="n">
         <v>50.42</v>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
+      <c r="K127" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="L127" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="M127" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
+      <c r="N127" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O127" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="P127" s="19" t="inlineStr">
         <is>
           <t>DASMXT010000124.1 / DASMXT010000213.1</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>mcr-1.1</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
+      <c r="Q127" s="19" t="inlineStr">
+        <is>
+          <t>mcr-1.1</t>
+        </is>
+      </c>
+      <c r="R127" s="19" t="inlineStr">
         <is>
           <t>mcr-1.1_1</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T127" s="19" t="inlineStr">
         <is>
           <t>chromosome / plasmid</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="U127" s="19" t="inlineStr">
         <is>
           <t>IncFIB, IncHI2A, rep_cluster_1088</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
+      <c r="V127" s="19" t="inlineStr">
         <is>
           <t>MOBH</t>
         </is>
       </c>
-      <c r="W127" t="n">
+      <c r="W127" s="19" t="n">
         <v>328273</v>
       </c>
-      <c r="X127" t="n">
+      <c r="X127" s="19" t="n">
         <v>226</v>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Y127" s="19" t="inlineStr">
         <is>
           <t>adk(10) fumC(27) gyrB(5) icd(8) mdh(8) purA(7) recA(2)</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="Z127" s="19" t="inlineStr">
         <is>
           <t>IncFIB(AP001918)_1, IncFII(pCoo)_1, IncHI2A_1, IncHI2_1, IncI1_1_Alpha</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>SAMN49772998</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t>GCA_053709775.1</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>B (GenBank assembly)</t>
         </is>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="19" t="n">
         <v>205</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="19" t="n">
         <v>5100318</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="19" t="n">
         <v>111077</v>
       </c>
-      <c r="I128" t="n">
+      <c r="I128" s="19" t="n">
         <v>50.51</v>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="K128" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L128" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
+      <c r="M128" s="19" t="inlineStr">
         <is>
           <t>ALLELEX</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="N128" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O128" s="19" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P128" s="19" t="inlineStr">
         <is>
           <t>JBSKJU010000076.1</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
+      <c r="Q128" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" s="19" t="inlineStr">
         <is>
           <t>mcr-9.1_1</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="T128" s="19" t="inlineStr">
         <is>
           <t>chromosome</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr">
+      <c r="V128" s="19" t="inlineStr">
         <is>
           <t>MOBP</t>
         </is>
       </c>
-      <c r="X128" t="n">
+      <c r="X128" s="19" t="n">
         <v>297</v>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Y128" s="19" t="inlineStr">
         <is>
           <t>adk(6) fumC(65) gyrB(32) icd(26) mdh(9) purA(8) recA(2)</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="Z128" s="19" t="inlineStr">
         <is>
           <t>IncI1_1_Alpha, IncI2_1</t>
         </is>
